--- a/XDI-CDIF-Mapping.xlsx
+++ b/XDI-CDIF-Mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/944a82e2ddcde9eb/Documents/GithubC/CDIF/integrationPublic/XrayAbsorbtion/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GithubC\CDIF\XAS-CDIF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="575" documentId="8_{653FF32C-26FE-4786-924B-BC9728C43172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46DC93BA-2D14-41F1-B922-EE0DD29D8F6D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACC9F732-A6CD-41CD-909F-5FE8466C4F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1089" yWindow="686" windowWidth="20494" windowHeight="10911" xr2:uid="{F15BBCC5-F362-4B5F-9E39-D6E36C713949}"/>
+    <workbookView xWindow="2310" yWindow="1560" windowWidth="25920" windowHeight="14775" xr2:uid="{F15BBCC5-F362-4B5F-9E39-D6E36C713949}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,13 +38,44 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Stephen Richard</author>
+  </authors>
+  <commentList>
+    <comment ref="A39" authorId="0" shapeId="0" xr:uid="{F904EBAC-ED46-42FD-A90A-3691974E7897}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Stephen Richard:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+aka…  beamline.xray_source</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="195">
   <si>
     <t>xdi dictionary</t>
-  </si>
-  <si>
-    <t>CDIF implementation</t>
   </si>
   <si>
     <t>facility</t>
@@ -514,15 +545,6 @@
     <t>"schema:keywords": [</t>
   </si>
   <si>
-    <t xml:space="preserve">{"@type": "schema:DefinedTerm",
-     "schema:termCode": "[[value]]",
-     "schema:inDefinedTermSet": "https://github.com/XraySpectroscopy/XAS-Data-Interchange/blob/master/specification/dictionary.md"   } </t>
-  </si>
-  <si>
-    <t>schema:location: {
-   "@type": ["schema:Place", "xas:Facility"]</t>
-  </si>
-  <si>
     <t xml:space="preserve">  "schema:name": "[[value]]"</t>
   </si>
   <si>
@@ -533,11 +555,6 @@
   </si>
   <si>
     <t>Provenance</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> "prov:wasGeneratedBy": {
-        "@type": [  "schema:Event",  "xas:Analysis_Event",     "prov:Activity"   ]
-       </t>
   </si>
   <si>
     <t>"schema:additionalProperty": [
@@ -590,38 +607,12 @@
   "schema:name": "Detector"  </t>
   </si>
   <si>
-    <t xml:space="preserve">{"@type": "schema:DefinedTerm",
-    "schema:termCode": "[[value]]",
-    "schema:inDefinedTermSet": "http://sweetontology.net/matrElement"} </t>
-  </si>
-  <si>
-    <t xml:space="preserve">{"@type": "schema:DefinedTerm",
-   "schema:termCode": "[[value]]",
-   "schema:inDefinedTermSet": "http://sweetontology.net/matrElement"      } </t>
-  </si>
-  <si>
-    <t>{  "@type": [ "schema:Thing",   "prov:Entity","xas:Beamline"   ],</t>
-  </si>
-  <si>
-    <t>{  "@type": ["schema:Thing", "xas:Monochromator"],</t>
-  </si>
-  <si>
     <t>{"@type": "schema:PropertyValue",
     "schema:propertyID": {"@id": "xas:facility_energy"},
      "schema:value": "[[value]]"  }</t>
   </si>
   <si>
     <t>"schema:additionalProperty": [</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    {  "@type": "schema:PropertyValue",
-        "schema:propertyID": {"@id": "xas:facility_energy"},
-          "schema:value": "[[value]]"     }</t>
-  </si>
-  <si>
-    <t>{"@type": "schema:PropertyValue",
-   "schema:propertyID": {"@id": "xas:facility_energy"},
-   "schema:value": "[[value]]"   }</t>
   </si>
   <si>
     <t xml:space="preserve">    {    "@type": "schema:PropertyValue",
@@ -869,12 +860,80 @@
            "cdi:name": "r" }
 </t>
   </si>
+  <si>
+    <t>CDIF implementation 1</t>
+  </si>
+  <si>
+    <t>CDIF implementation 2</t>
+  </si>
+  <si>
+    <t>CDIF implementation 3</t>
+  </si>
+  <si>
+    <t>CDIF implementation 4</t>
+  </si>
+  <si>
+    <t>Entity</t>
+  </si>
+  <si>
+    <t>source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    {  "@type": "schema:PropertyValue",
+        "schema:propertyID": {"@id": "xas:facility_xray_source"},
+          "schema:value": "[[value]]"     }</t>
+  </si>
+  <si>
+    <t>{"@type": "schema:PropertyValue",
+   "schema:propertyID": {"@id": "xas:facility_current"},
+   "schema:value": "[[value]]"   }</t>
+  </si>
+  <si>
+    <t>{  "@type": ["schema:Thing"],"schema:additionalType":[ "xas:Monochromator"],</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{"@type": "schema:DefinedTerm",
+     "schema:termCode": "[[value]]",
+     "schema:inDefinedTermSet": "https://github.com/XraySpectroscopy/XAS-Data-Interchange/blob/master/specification/dictionary.md" ,
+     "schema:about":"element.ref_edge" } </t>
+  </si>
+  <si>
+    <t xml:space="preserve">{"@type": "schema:DefinedTerm",
+     "schema:termCode": "[[value]]",
+     "schema:inDefinedTermSet": "https://github.com/XraySpectroscopy/XAS-Data-Interchange/blob/master/specification/dictionary.md",
+     "schema:about":"element.edge" } </t>
+  </si>
+  <si>
+    <t xml:space="preserve">{"@type": "schema:DefinedTerm",
+   "schema:termCode": "[[value]]",
+   "schema:inDefinedTermSet": "http://sweetontology.net/matrElement" ,
+     "schema:about":"element.reference"  } </t>
+  </si>
+  <si>
+    <t xml:space="preserve">{"@type": "schema:DefinedTerm",
+    "schema:termCode": "[[value]]",
+    "schema:inDefinedTermSet": "http://sweetontology.net/matrElement",
+     "schema:about":"element.symbol" } </t>
+  </si>
+  <si>
+    <t>schema:location: {
+   "@type": ["schema:Place"], "schema:additionalType":["xas:Facility"]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> "prov:wasGeneratedBy": {
+        "@type": [  "schema:Action",   "prov:Activity" ],    
+         "schema:additionalType": [ "xas:Analysis_Event"], 
+       </t>
+  </si>
+  <si>
+    <t>{  "@type": [ "schema:Thing",   "prov:Entity"], "schema:additionalType": ["xas:Beamline" ],</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -937,13 +996,75 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="9"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.5"/>
+      <color theme="9"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -958,7 +1079,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -987,6 +1108,21 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1002,10 +1138,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1324,1258 +1456,1274 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8B05E63-C949-4A97-A85C-3FA47FECF3CD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8B05E63-C949-4A97-A85C-3FA47FECF3CD}">
   <dimension ref="A1:I93"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.23046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.23046875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.3828125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.15234375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="63.921875" style="1" customWidth="1"/>
-    <col min="6" max="7" width="9.07421875" style="1"/>
-    <col min="8" max="8" width="17.53515625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="20.84375" customWidth="1"/>
+    <col min="1" max="1" width="33.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="73.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="41" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="59.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.5703125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>181</v>
+      </c>
       <c r="E1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="72.900000000000006" x14ac:dyDescent="0.4">
+        <v>182</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="102" x14ac:dyDescent="0.4">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="165" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A4" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="F4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A5" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A6" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="20.6" x14ac:dyDescent="0.4">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="21" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="29.15" x14ac:dyDescent="0.4">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B9" s="8"/>
       <c r="D9" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="54.9" x14ac:dyDescent="0.4">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="71.25" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="57" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="57" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="57" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="57" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="57" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="57" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="57" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="57" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="57" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="71.25" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
         <v>102</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="54.9" x14ac:dyDescent="0.4">
-      <c r="A11" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="54.9" x14ac:dyDescent="0.4">
-      <c r="A12" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="68.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A13" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="54.9" x14ac:dyDescent="0.4">
-      <c r="A14" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="54.9" x14ac:dyDescent="0.4">
-      <c r="A15" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="68.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A16" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A17" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="54.9" x14ac:dyDescent="0.4">
-      <c r="A18" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="54.9" x14ac:dyDescent="0.4">
-      <c r="A19" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="54.9" x14ac:dyDescent="0.4">
-      <c r="A20" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="54.9" x14ac:dyDescent="0.4">
-      <c r="A21" s="8" t="s">
-        <v>103</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="68.599999999999994" x14ac:dyDescent="0.4">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="71.25" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="71.25" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="68.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A23" s="1" t="s">
+      <c r="F23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="71.25" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="71.25" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="68.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A24" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="E25" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="68.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A25" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="F25" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="27.45" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="85.5" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B26" s="6"/>
       <c r="D26" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="68.599999999999994" x14ac:dyDescent="0.4">
-      <c r="A27" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="71.25" x14ac:dyDescent="0.25">
+      <c r="A27" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A28" s="1" t="s">
+      <c r="E28" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" spans="1:7" ht="99.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="99.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="71.25" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="71.25" x14ac:dyDescent="0.25">
+      <c r="A33" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D34" s="2"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C36" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37" spans="1:7" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E39" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="A43" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C44" t="s">
         <v>115</v>
       </c>
-      <c r="F28" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="18.45" x14ac:dyDescent="0.4">
-      <c r="A29" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E29" s="2"/>
-    </row>
-    <row r="30" spans="1:7" ht="82.3" x14ac:dyDescent="0.4">
-      <c r="A30" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="82.3" x14ac:dyDescent="0.4">
-      <c r="A31" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="54.9" x14ac:dyDescent="0.4">
-      <c r="A32" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="54.9" x14ac:dyDescent="0.4">
-      <c r="A33" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="41.15" x14ac:dyDescent="0.4">
-      <c r="A34" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D34" s="2"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A35" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="C36" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="E36" s="2"/>
-    </row>
-    <row r="37" spans="1:7" ht="41.15" x14ac:dyDescent="0.4">
-      <c r="A37" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="54.9" x14ac:dyDescent="0.4">
-      <c r="A38" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="54.9" x14ac:dyDescent="0.4">
-      <c r="A39" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A40" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A41" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A42" s="1" t="s">
+      <c r="F44" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="G42" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="116.6" x14ac:dyDescent="0.4">
-      <c r="A43" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A44" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C44" t="s">
-        <v>116</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A45" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="C45" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="20.6" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="21" x14ac:dyDescent="0.25">
       <c r="A46" s="6"/>
       <c r="C46" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="58.3" x14ac:dyDescent="0.4">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="43.75" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="43.75" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="1" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="43.75" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="1" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="43.75" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="E51" s="1" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="43.75" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="1" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="43.75" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="1" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="43.75" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="1" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="43.75" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="1" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="43.75" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="1" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="43.75" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="1" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="43.75" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="43.75" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="1" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="43.75" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="1" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="43.75" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="43.75" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="43.75" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="1" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="43.75" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="1" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" ht="43.75" x14ac:dyDescent="0.4">
-      <c r="A65" s="1" t="s">
-        <v>67</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A65" s="13" t="s">
+        <v>66</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" ht="43.75" x14ac:dyDescent="0.4">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.4">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="87.45" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="C68" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" ht="18.45" x14ac:dyDescent="0.4">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
       <c r="E70" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" ht="218.6" x14ac:dyDescent="0.4">
-      <c r="A71" s="5" t="s">
-        <v>3</v>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="210" x14ac:dyDescent="0.25">
+      <c r="A71" s="12" t="s">
+        <v>2</v>
       </c>
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
       <c r="D71" s="5"/>
       <c r="E71" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G71" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+      <c r="A72" s="5" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" ht="116.6" x14ac:dyDescent="0.4">
-      <c r="A72" s="5" t="s">
-        <v>28</v>
       </c>
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
       <c r="D72" s="5"/>
       <c r="E72" s="1" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="189.45" x14ac:dyDescent="0.4">
-      <c r="A73" s="5" t="s">
-        <v>8</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="180" x14ac:dyDescent="0.25">
+      <c r="A73" s="12" t="s">
+        <v>7</v>
       </c>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
       <c r="D73" s="5"/>
       <c r="E73" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" ht="160.30000000000001" x14ac:dyDescent="0.4">
-      <c r="A74" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="150" x14ac:dyDescent="0.25">
+      <c r="A74" s="12" t="s">
+        <v>28</v>
       </c>
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
       <c r="D74" s="5"/>
       <c r="E74" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" ht="174.9" x14ac:dyDescent="0.4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="165" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
       <c r="D75" s="5"/>
       <c r="E75" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" ht="116.6" x14ac:dyDescent="0.4">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
       <c r="D76" s="5"/>
       <c r="E76" s="1" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" ht="116.6" x14ac:dyDescent="0.4">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
       <c r="D77" s="5"/>
       <c r="E77" s="1" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" ht="116.6" x14ac:dyDescent="0.4">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
       <c r="D78" s="5"/>
       <c r="E78" s="1" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" ht="116.6" x14ac:dyDescent="0.4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
       <c r="D79" s="5"/>
       <c r="E79" s="1" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" ht="131.15" x14ac:dyDescent="0.4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="120" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
       <c r="D80" s="5"/>
       <c r="E80" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" ht="131.15" x14ac:dyDescent="0.4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
       <c r="D81" s="5"/>
       <c r="E81" s="1" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" ht="131.15" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
       <c r="D82" s="5"/>
       <c r="E82" s="1" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" ht="131.15" x14ac:dyDescent="0.4">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
       <c r="D83" s="5"/>
       <c r="E83" s="1" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" ht="131.15" x14ac:dyDescent="0.4">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B84" s="5"/>
       <c r="C84" s="5"/>
       <c r="D84" s="5"/>
       <c r="E84" s="1" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" ht="131.15" x14ac:dyDescent="0.4">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B85" s="5"/>
       <c r="C85" s="5"/>
       <c r="D85" s="5"/>
       <c r="E85" s="1" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" ht="131.15" x14ac:dyDescent="0.4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B86" s="5"/>
       <c r="C86" s="5"/>
       <c r="D86" s="5"/>
       <c r="E86" s="1" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I86" s="1"/>
     </row>
-    <row r="87" spans="1:9" ht="131.15" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B87" s="5"/>
       <c r="C87" s="5"/>
       <c r="D87" s="5"/>
       <c r="E87" s="1" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I87" s="1"/>
     </row>
-    <row r="88" spans="1:9" ht="131.15" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B88" s="5"/>
       <c r="C88" s="5"/>
       <c r="D88" s="5"/>
       <c r="E88" s="1" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I88" s="1"/>
     </row>
-    <row r="89" spans="1:9" ht="131.15" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:9" ht="120" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B89" s="5"/>
       <c r="C89" s="5"/>
       <c r="D89" s="5"/>
       <c r="E89" s="1" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I89" s="1"/>
     </row>
-    <row r="90" spans="1:9" ht="23.6" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:9" ht="24" x14ac:dyDescent="0.25">
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
       <c r="C90" s="7"/>
       <c r="D90" s="7"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="5"/>
       <c r="B91" s="5"/>
       <c r="C91" s="5"/>
       <c r="D91" s="5"/>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="5"/>
       <c r="B92" s="5"/>
       <c r="C92" s="5"/>
       <c r="D92" s="5"/>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="5"/>
       <c r="B93" s="5"/>
       <c r="C93" s="5"/>
@@ -2587,5 +2735,6 @@
     <sortCondition ref="A10:A68"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>